--- a/tools/excel-config/tuning.xlsx
+++ b/tools/excel-config/tuning.xlsx
@@ -456,13 +456,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -814,11 +814,11 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>rowSpawnInterval</t>
+          <t>rowGapCells</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -827,18 +827,18 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>行入场间隔 秒</t>
+          <t>相邻两行的纵向间距（格）：行间隔 = 该值 × cellSize ÷ 当前波下落速度</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>bandSpawnInterval</t>
+          <t>spawnStaggerBudget</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>带入场间隔 秒</t>
+          <t>带内弹出允许占用一个行间隔的比例</t>
         </is>
       </c>
     </row>
@@ -914,91 +914,91 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>difficultyRowPerWave</t>
+          <t>hitFlashTime</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1</v>
+        <v>0.12</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>难度</t>
+          <t>反馈</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>每波行数增量</t>
+          <t>受击闪白持续时间 秒</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>difficultyRowMax</t>
+          <t>hitFlashAlpha</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>难度</t>
+          <t>反馈</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>单波行数上限</t>
+          <t>受击闪白起始不透明度 0~255</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>difficultySpeedGrowth</t>
+          <t>hitShakeTime</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>难度</t>
+          <t>反馈</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>每波下移速度增幅</t>
+          <t>敌人受击震动持续时间 秒</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>difficultySpeedMax</t>
+          <t>hitShakeAmplitude</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>难度</t>
+          <t>反馈</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>下移速度倍率上限</t>
+          <t>敌人受击震动幅度 px（随时间衰减）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>difficultyHpGrowth</t>
+          <t>difficultyRowPerWave</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -1007,18 +1007,18 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>每波血量增幅</t>
+          <t>每波行数增量</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>difficultyHpMax</t>
+          <t>difficultyRowMax</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2.5</v>
+        <v>30</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -1027,18 +1027,18 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>血量倍率上限</t>
+          <t>单波行数上限</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>attackRatioWave1</t>
+          <t>difficultySpeedGrowth</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -1047,18 +1047,18 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>第 1 波攻击型占比</t>
+          <t>每波下移速度增幅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>attackRatioWave4</t>
+          <t>difficultySpeedMax</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -1067,18 +1067,18 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>第 4 波攻击型占比</t>
+          <t>下移速度倍率上限</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>attackRatioWave8</t>
+          <t>difficultyHpGrowth</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -1087,18 +1087,18 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>第 8 波攻击型占比</t>
+          <t>每波血量增幅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>attackRatioWave15</t>
+          <t>difficultyHpMax</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>0.35</v>
+        <v>2.5</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -1107,18 +1107,18 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>第 15 波攻击型占比</t>
+          <t>血量倍率上限</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>attackRatioWave16</t>
+          <t>attackRatioWave1</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
@@ -1127,98 +1127,98 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>第 16 波及以后攻击型占比（封顶）</t>
+          <t>第 1 波攻击型占比</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>dropScatterRadius</t>
+          <t>attackRatioWave4</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>16</v>
+        <v>0.1</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>掉落</t>
+          <t>难度</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>散落半径 px（0.2 格）</t>
+          <t>第 4 波攻击型占比</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>dropMagnetRadius</t>
+          <t>attackRatioWave8</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>120</v>
+        <v>0.2</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>掉落</t>
+          <t>难度</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>磁吸半径 px（1.5 格）</t>
+          <t>第 8 波攻击型占比</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>dropLifeTime</t>
+          <t>attackRatioWave15</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>15</v>
+        <v>0.35</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>掉落</t>
+          <t>难度</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>掉落物存活 秒</t>
+          <t>第 15 波攻击型占比</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>dropMaxOnScreen</t>
+          <t>attackRatioWave16</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>80</v>
+        <v>0.5</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>掉落</t>
+          <t>难度</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>同屏掉落物上限</t>
+          <t>第 16 波及以后攻击型占比（封顶）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>dropBossCrystalCount</t>
+          <t>dropScatterRadius</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
@@ -1227,98 +1227,98 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>大BOSS 经验水晶颗数（按占格 2~4）</t>
+          <t>散落半径 px（0.2 格）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>coinRerollBase</t>
+          <t>dropMagnetRadius</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>经济</t>
+          <t>掉落</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>刷新候选首次价格</t>
+          <t>磁吸半径 px（1.5 格）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>coinRerollStep</t>
+          <t>dropLifeTime</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>经济</t>
+          <t>掉落</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>刷新候选每次涨价</t>
+          <t>掉落物存活 秒</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>coinBuyCommon</t>
+          <t>dropMaxOnScreen</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>经济</t>
+          <t>掉落</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>购买普通技能价格</t>
+          <t>同屏掉落物上限</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>coinBuyRare</t>
+          <t>dropBossCrystalCount</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>经济</t>
+          <t>掉落</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>购买稀有技能价格</t>
+          <t>大BOSS 经验水晶颗数（按占格 2~4）</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>coinBuyEpic</t>
+          <t>coinRerollBase</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
@@ -1327,18 +1327,18 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>购买史诗技能价格</t>
+          <t>刷新候选首次价格</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>coinBuyLegendary</t>
+          <t>coinRerollStep</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
@@ -1347,18 +1347,18 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>购买传说技能价格</t>
+          <t>刷新候选每次涨价</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>coinBuyGrowthPerWave</t>
+          <t>coinBuyCommon</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>0.05</v>
+        <v>60</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
@@ -1367,18 +1367,18 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>价格随波数上浮系数</t>
+          <t>购买普通技能价格</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>coinBuySuperCrystal</t>
+          <t>coinBuyRare</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
@@ -1387,18 +1387,18 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>购买超级水晶价格</t>
+          <t>购买稀有技能价格</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>expCurveBase</t>
+          <t>coinBuyEpic</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>8</v>
+        <v>220</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
@@ -1407,18 +1407,18 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>经验曲线常数项</t>
+          <t>购买史诗技能价格</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>expCurveLinear</t>
+          <t>coinBuyLegendary</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>6</v>
+        <v>400</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
@@ -1427,18 +1427,18 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>经验曲线一次项</t>
+          <t>购买传说技能价格</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>expCurveQuad</t>
+          <t>coinBuyGrowthPerWave</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>1.5</v>
+        <v>0.05</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
@@ -1447,98 +1447,98 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>经验曲线二次项</t>
+          <t>价格随波数上浮系数</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>talentOfferCount</t>
+          <t>coinBuySuperCrystal</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>经济</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>开局天赋候选数</t>
+          <t>购买超级水晶价格</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>levelUpOfferCount</t>
+          <t>expCurveBase</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>经济</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>升级候选数</t>
+          <t>经验曲线常数项</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>rarityWeightCommon</t>
+          <t>expCurveLinear</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>经济</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>普通技能权重</t>
+          <t>经验曲线一次项</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>rarityWeightRare</t>
+          <t>expCurveQuad</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>30</v>
+        <v>1.5</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>经济</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>稀有技能权重</t>
+          <t>经验曲线二次项</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>rarityWeightEpic</t>
+          <t>talentOfferCount</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
@@ -1547,14 +1547,14 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>史诗技能权重</t>
+          <t>开局天赋候选数</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>rarityWeightLegendary</t>
+          <t>levelUpOfferCount</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
@@ -1567,18 +1567,18 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>传说技能权重</t>
+          <t>升级候选数</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>legendaryMaxPerRun</t>
+          <t>rarityWeightCommon</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
@@ -1587,18 +1587,18 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>传说卡每局最多出现次数</t>
+          <t>普通技能权重</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>superCrystalUpgradeCost</t>
+          <t>rarityWeightRare</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
@@ -1607,18 +1607,18 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>超级水晶：升级技能消耗</t>
+          <t>稀有技能权重</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>superCrystalEvolveCost</t>
+          <t>rarityWeightEpic</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
@@ -1627,18 +1627,18 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>超级水晶：进化消耗</t>
+          <t>史诗技能权重</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>superCrystalFuseCost</t>
+          <t>rarityWeightLegendary</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
@@ -1647,98 +1647,98 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>超级水晶：融合消耗</t>
+          <t>传说技能权重</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>metaCostBase</t>
+          <t>legendaryMaxPerRun</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>外围</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>加点成本系数</t>
+          <t>传说卡每局最多出现次数</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>metaCostPow</t>
+          <t>superCrystalUpgradeCost</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>外围</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>加点成本指数</t>
+          <t>超级水晶：升级技能消耗</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>gachaCost</t>
+          <t>superCrystalEvolveCost</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>外围</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>召唤单次消耗魂晶</t>
+          <t>超级水晶：进化消耗</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>gachaPity</t>
+          <t>superCrystalFuseCost</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>外围</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>召唤保底次数</t>
+          <t>超级水晶：融合消耗</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>gachaReturnRate</t>
+          <t>metaCostBase</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
@@ -1747,145 +1747,225 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>重复皮肤返还魂晶比例</t>
+          <t>加点成本系数</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>damageTextMaxOnScreen</t>
+          <t>metaCostPow</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>12</v>
+        <v>1.4</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>表现</t>
+          <t>外围</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>同屏伤害数字上限</t>
+          <t>加点成本指数</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>deathFxMaxOnScreen</t>
+          <t>gachaCost</t>
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>表现</t>
+          <t>外围</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>同屏击杀特效上限</t>
+          <t>召唤单次消耗魂晶</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>hudHpBarWidth</t>
+          <t>gachaPity</t>
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>520</v>
+        <v>10</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>表现</t>
+          <t>外围</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>血条宽</t>
+          <t>召唤保底次数</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>hudHpBarHeight</t>
+          <t>gachaReturnRate</t>
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>26</v>
+        <v>0.5</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>表现</t>
+          <t>外围</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>血条高</t>
+          <t>重复皮肤返还魂晶比例</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>maxSubStepDistance</t>
+          <t>damageTextMaxOnScreen</t>
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>性能</t>
+          <t>表现</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>子弹单子步最大位移 px（防穿模）</t>
+          <t>同屏伤害数字上限</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>maxSubStepCount</t>
+          <t>deathFxMaxOnScreen</t>
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>性能</t>
+          <t>表现</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>单帧最大子步数</t>
+          <t>同屏击杀特效上限</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
+          <t>hudHpBarWidth</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>520</v>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>表现</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>血条宽</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>hudHpBarHeight</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>表现</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>血条高</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>maxSubStepDistance</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>性能</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>子弹单子步最大位移 px（防穿模）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>maxSubStepCount</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>性能</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>单帧最大子步数</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
           <t>maxFrameDt</t>
         </is>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B75" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>性能</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>单帧最大推进时长 秒（掉帧/切后台夹紧）</t>
         </is>

--- a/tools/excel-config/tuning.xlsx
+++ b/tools/excel-config/tuning.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>格尺寸 px（体型与散落距离的基准）</t>
+          <t>格尺寸 px（= 品质底图素材尺寸，体型与散落距离的基准）</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>700</v>
+        <v>1120</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>散落半径 px（0.2 格）</t>
+          <t>散落半径 px（0.2 格 = 25.6）</t>
         </is>
       </c>
     </row>
@@ -1968,6 +1968,26 @@
       <c r="D75" s="4" t="inlineStr">
         <is>
           <t>单帧最大推进时长 秒（掉帧/切后台夹紧）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>artFitMargin</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>美术</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>怪物/玩家图在占格内的留白系数（contain 适配）</t>
         </is>
       </c>
     </row>
